--- a/exports/trend_1d/BHARTIARTL_full_report.xlsx
+++ b/exports/trend_1d/BHARTIARTL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.84</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="H2" t="n">
-        <v>349.55</v>
+        <v>346.2</v>
       </c>
       <c r="I2" t="n">
         <v>348.34529676545</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="L2" t="n">
         <v>2.93</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.24</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42073</v>
+        <v>42074</v>
       </c>
       <c r="H3" t="n">
-        <v>361.15</v>
+        <v>382.35</v>
       </c>
       <c r="I3" t="n">
         <v>366.3181645572929</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.32</v>
+        <v>-10.44</v>
       </c>
       <c r="L3" t="n">
-        <v>8.390000000000001</v>
+        <v>11.71</v>
       </c>
       <c r="M3" t="n">
         <v>1.41</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.55</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42212</v>
+        <v>42213</v>
       </c>
       <c r="H4" t="n">
-        <v>410.25</v>
+        <v>402.45</v>
       </c>
       <c r="I4" t="n">
         <v>404.5640447956092</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K4" t="n">
-        <v>7.3</v>
+        <v>5.26</v>
       </c>
       <c r="L4" t="n">
         <v>7.01</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.08</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42293</v>
+        <v>42296</v>
       </c>
       <c r="H5" t="n">
-        <v>343.2</v>
+        <v>357</v>
       </c>
       <c r="I5" t="n">
         <v>347.088343478896</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K5" t="n">
-        <v>14.72</v>
+        <v>11.29</v>
       </c>
       <c r="L5" t="n">
         <v>4.31</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>10.6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H6" t="n">
-        <v>340</v>
+        <v>330.35</v>
       </c>
       <c r="I6" t="n">
         <v>332.1789962179461</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.76</v>
+        <v>-7.46</v>
       </c>
       <c r="L6" t="n">
-        <v>5.63</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="N6" t="n">
         <v>3.33</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.45</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42360</v>
+        <v>42361</v>
       </c>
       <c r="H7" t="n">
-        <v>317.25</v>
+        <v>326.25</v>
       </c>
       <c r="I7" t="n">
         <v>324.9289965458667</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="n">
-        <v>3.97</v>
+        <v>1.24</v>
       </c>
       <c r="L7" t="n">
         <v>2.86</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42380</v>
+        <v>42381</v>
       </c>
       <c r="H8" t="n">
-        <v>315.25</v>
+        <v>309.6</v>
       </c>
       <c r="I8" t="n">
         <v>311.582138251086</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.37</v>
+        <v>-5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>5.32</v>
+        <v>5.66</v>
       </c>
       <c r="M8" t="n">
         <v>0.88</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>10.13</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42411</v>
+        <v>42412</v>
       </c>
       <c r="H9" t="n">
-        <v>303</v>
+        <v>318.55</v>
       </c>
       <c r="I9" t="n">
         <v>317.8470600199097</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9" t="n">
-        <v>2.13</v>
+        <v>-2.89</v>
       </c>
       <c r="L9" t="n">
-        <v>3.18</v>
+        <v>4.62</v>
       </c>
       <c r="M9" t="n">
         <v>1.78</v>
       </c>
       <c r="N9" t="n">
-        <v>3.36</v>
+        <v>5.13</v>
       </c>
       <c r="O9" t="n">
         <v>-1.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42592</v>
+        <v>42593</v>
       </c>
       <c r="H10" t="n">
-        <v>340.05</v>
+        <v>339.95</v>
       </c>
       <c r="I10" t="n">
         <v>339.9589868608036</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K10" t="n">
-        <v>6.75</v>
+        <v>6.72</v>
       </c>
       <c r="L10" t="n">
         <v>5.24</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.92</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42702</v>
+        <v>42703</v>
       </c>
       <c r="H11" t="n">
-        <v>312.9</v>
+        <v>318.85</v>
       </c>
       <c r="I11" t="n">
         <v>315.4509954296693</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K11" t="n">
-        <v>7.96</v>
+        <v>6.21</v>
       </c>
       <c r="L11" t="n">
         <v>3.47</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.74</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42720</v>
+        <v>42723</v>
       </c>
       <c r="H12" t="n">
-        <v>304.55</v>
+        <v>299.85</v>
       </c>
       <c r="I12" t="n">
         <v>300.3718463336683</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.48</v>
+        <v>-5.96</v>
       </c>
       <c r="L12" t="n">
-        <v>5.05</v>
+        <v>6.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H13" t="n">
-        <v>308.1</v>
+        <v>315.2</v>
       </c>
       <c r="I13" t="n">
         <v>311.4288092181267</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.75</v>
+        <v>-5.12</v>
       </c>
       <c r="L13" t="n">
-        <v>3.18</v>
+        <v>5.74</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.48</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42815</v>
+        <v>42816</v>
       </c>
       <c r="H14" t="n">
-        <v>343.45</v>
+        <v>331.95</v>
       </c>
       <c r="I14" t="n">
         <v>337.7444894619188</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K14" t="n">
-        <v>8.960000000000001</v>
+        <v>5.31</v>
       </c>
       <c r="L14" t="n">
         <v>5.01</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>10.36</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42864</v>
+        <v>42865</v>
       </c>
       <c r="H15" t="n">
-        <v>338.9</v>
+        <v>365.9</v>
       </c>
       <c r="I15" t="n">
         <v>357.9215945053693</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.09</v>
+        <v>-10.23</v>
       </c>
       <c r="L15" t="n">
-        <v>7.03</v>
+        <v>12.49</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>7.97</v>
       </c>
       <c r="O15" t="n">
         <v>-3.35</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.54</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42983</v>
+        <v>42984</v>
       </c>
       <c r="H16" t="n">
-        <v>399</v>
+        <v>395.1</v>
       </c>
       <c r="I16" t="n">
         <v>398.3780274366977</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K16" t="n">
-        <v>9.050000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="L16" t="n">
         <v>9.73</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>7.3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43020</v>
+        <v>43021</v>
       </c>
       <c r="H17" t="n">
-        <v>392.85</v>
+        <v>422.95</v>
       </c>
       <c r="I17" t="n">
         <v>399.7516167087609</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" t="n">
-        <v>0.57</v>
+        <v>-7.05</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>8.57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2</v>
+        <v>7.45</v>
       </c>
       <c r="N17" t="n">
-        <v>4.93</v>
+        <v>7.66</v>
       </c>
       <c r="O17" t="n">
         <v>-0.98</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H18" t="n">
-        <v>488.95</v>
+        <v>477.8</v>
       </c>
       <c r="I18" t="n">
         <v>479.0011468756942</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" t="n">
-        <v>15.6</v>
+        <v>12.97</v>
       </c>
       <c r="L18" t="n">
         <v>2.34</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>12.16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43076</v>
+        <v>43077</v>
       </c>
       <c r="H19" t="n">
-        <v>505.2</v>
+        <v>515.45</v>
       </c>
       <c r="I19" t="n">
         <v>513.5490948022625</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.73</v>
+        <v>-7.88</v>
       </c>
       <c r="L19" t="n">
-        <v>6.52</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>9.17</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H20" t="n">
-        <v>483.05</v>
+        <v>451.05</v>
       </c>
       <c r="I20" t="n">
         <v>479.2851834956884</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.29</v>
+        <v>-12.49</v>
       </c>
       <c r="L20" t="n">
-        <v>7.93</v>
+        <v>13.33</v>
       </c>
       <c r="M20" t="n">
         <v>2.48</v>
       </c>
       <c r="N20" t="n">
-        <v>4.38</v>
+        <v>6.62</v>
       </c>
       <c r="O20" t="n">
         <v>2.03</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.57</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43214</v>
+        <v>43215</v>
       </c>
       <c r="H21" t="n">
-        <v>398.75</v>
+        <v>412.1</v>
       </c>
       <c r="I21" t="n">
         <v>403.070956765194</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K21" t="n">
-        <v>11.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>5.97</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>8.68</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H22" t="n">
-        <v>379.5</v>
+        <v>376.1</v>
       </c>
       <c r="I22" t="n">
         <v>376.3317079091737</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.91</v>
+        <v>-8.74</v>
       </c>
       <c r="L22" t="n">
-        <v>9.140000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>2.89</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.52</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H23" t="n">
-        <v>358</v>
+        <v>376.2</v>
       </c>
       <c r="I23" t="n">
         <v>360.6066808155925</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K23" t="n">
-        <v>4.81</v>
+        <v>-0.03</v>
       </c>
       <c r="L23" t="n">
         <v>2.83</v>
@@ -1752,7 +2027,7 @@
         <v>1.79</v>
       </c>
       <c r="N23" t="n">
-        <v>4.24</v>
+        <v>5.08</v>
       </c>
       <c r="O23" t="n">
         <v>-0.9</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>13.62</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H24" t="n">
-        <v>350.2</v>
+        <v>332.3</v>
       </c>
       <c r="I24" t="n">
         <v>348.5811737817425</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.91</v>
+        <v>-11.67</v>
       </c>
       <c r="L24" t="n">
-        <v>10.25</v>
+        <v>12.56</v>
       </c>
       <c r="M24" t="n">
         <v>1.76</v>
       </c>
       <c r="N24" t="n">
-        <v>4.73</v>
+        <v>5.11</v>
       </c>
       <c r="O24" t="n">
         <v>5.08</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>15.81</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43419</v>
+        <v>43420</v>
       </c>
       <c r="H25" t="n">
-        <v>298.8</v>
+        <v>326.6</v>
       </c>
       <c r="I25" t="n">
         <v>315.4556807696867</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" t="n">
-        <v>10.08</v>
+        <v>1.72</v>
       </c>
       <c r="L25" t="n">
         <v>6.05</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>17.62</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43444</v>
+        <v>43445</v>
       </c>
       <c r="H26" t="n">
-        <v>289.5</v>
+        <v>284.9</v>
       </c>
       <c r="I26" t="n">
         <v>285.7506372625714</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
-        <v>-11.36</v>
+        <v>-12.77</v>
       </c>
       <c r="L26" t="n">
-        <v>12.58</v>
+        <v>15.25</v>
       </c>
       <c r="M26" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="N26" t="n">
         <v>4.28</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43472</v>
+        <v>43473</v>
       </c>
       <c r="H27" t="n">
-        <v>318.95</v>
+        <v>323.2</v>
       </c>
       <c r="I27" t="n">
         <v>320.4518637219093</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K27" t="n">
-        <v>-11.95</v>
+        <v>-13.44</v>
       </c>
       <c r="L27" t="n">
         <v>14.86</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.37</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43486</v>
+        <v>43487</v>
       </c>
       <c r="H28" t="n">
-        <v>305.6</v>
+        <v>299.25</v>
       </c>
       <c r="I28" t="n">
         <v>301.2348612983586</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.45</v>
+        <v>-7.41</v>
       </c>
       <c r="L28" t="n">
-        <v>7.58</v>
+        <v>8.42</v>
       </c>
       <c r="M28" t="n">
         <v>0.49</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>12</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H29" t="n">
-        <v>303</v>
+        <v>327.65</v>
       </c>
       <c r="I29" t="n">
         <v>325.1471863200185</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.25</v>
+        <v>-9.49</v>
       </c>
       <c r="L29" t="n">
-        <v>7.23</v>
+        <v>10.58</v>
       </c>
       <c r="M29" t="n">
         <v>1.48</v>
       </c>
       <c r="N29" t="n">
-        <v>1.94</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O29" t="n">
         <v>-2.08</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>12.55</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H30" t="n">
-        <v>342.95</v>
+        <v>310.65</v>
       </c>
       <c r="I30" t="n">
         <v>317.2181462614776</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K30" t="n">
-        <v>4.67</v>
+        <v>-5.19</v>
       </c>
       <c r="L30" t="n">
         <v>7.52</v>
       </c>
       <c r="M30" t="n">
-        <v>0.93</v>
+        <v>6.98</v>
       </c>
       <c r="N30" t="n">
-        <v>3.98</v>
+        <v>9.42</v>
       </c>
       <c r="O30" t="n">
         <v>8.140000000000001</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>16.39</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43623</v>
+        <v>43626</v>
       </c>
       <c r="H31" t="n">
-        <v>350.5</v>
+        <v>356.75</v>
       </c>
       <c r="I31" t="n">
         <v>352.8954177853761</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.83</v>
+        <v>-14.84</v>
       </c>
       <c r="L31" t="n">
-        <v>14.37</v>
+        <v>15.23</v>
       </c>
       <c r="M31" t="n">
         <v>1.97</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.67</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H32" t="n">
-        <v>337.25</v>
+        <v>332.65</v>
       </c>
       <c r="I32" t="n">
         <v>332.8079503080246</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.47</v>
+        <v>-6.76</v>
       </c>
       <c r="L32" t="n">
         <v>8.02</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.48</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43682</v>
+        <v>43683</v>
       </c>
       <c r="H33" t="n">
-        <v>351.1</v>
+        <v>361.65</v>
       </c>
       <c r="I33" t="n">
         <v>353.1962357062936</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.55</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>6.72</v>
+        <v>10.78</v>
       </c>
       <c r="M33" t="n">
         <v>2.5</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43896</v>
+        <v>43899</v>
       </c>
       <c r="H34" t="n">
-        <v>509.6</v>
+        <v>487.1</v>
       </c>
       <c r="I34" t="n">
         <v>506.9085940269667</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K34" t="n">
-        <v>40.91</v>
+        <v>34.69</v>
       </c>
       <c r="L34" t="n">
         <v>11.65</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>12.07</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43951</v>
+        <v>43955</v>
       </c>
       <c r="H35" t="n">
-        <v>504.8</v>
+        <v>522.7</v>
       </c>
       <c r="I35" t="n">
         <v>513.4961256503829</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.63</v>
+        <v>-7.31</v>
       </c>
       <c r="L35" t="n">
-        <v>8</v>
+        <v>8.82</v>
       </c>
       <c r="M35" t="n">
         <v>4.25</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>16.28</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44055</v>
+        <v>44056</v>
       </c>
       <c r="H36" t="n">
-        <v>537.6</v>
+        <v>525.5</v>
       </c>
       <c r="I36" t="n">
         <v>527.5645933451156</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K36" t="n">
-        <v>2.85</v>
+        <v>0.54</v>
       </c>
       <c r="L36" t="n">
         <v>6.12</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44131</v>
+        <v>44132</v>
       </c>
       <c r="H37" t="n">
-        <v>425.35</v>
+        <v>443.5</v>
       </c>
       <c r="I37" t="n">
         <v>436.2275998764891</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K37" t="n">
-        <v>19.06</v>
+        <v>15.6</v>
       </c>
       <c r="L37" t="n">
         <v>4.41</v>
       </c>
       <c r="M37" t="n">
-        <v>1.47</v>
+        <v>2.93</v>
       </c>
       <c r="N37" t="n">
         <v>6.46</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44253</v>
+        <v>44256</v>
       </c>
       <c r="H38" t="n">
-        <v>546.05</v>
+        <v>522.4</v>
       </c>
       <c r="I38" t="n">
         <v>538.3770499643457</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K38" t="n">
-        <v>23.12</v>
+        <v>17.79</v>
       </c>
       <c r="L38" t="n">
         <v>4.72</v>
@@ -2607,7 +3062,7 @@
         <v>0.91</v>
       </c>
       <c r="N38" t="n">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="O38" t="n">
         <v>4.27</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>12.6</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44316</v>
+        <v>44319</v>
       </c>
       <c r="H39" t="n">
-        <v>526.85</v>
+        <v>548.55</v>
       </c>
       <c r="I39" t="n">
         <v>544.9340862469445</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.85</v>
+        <v>-5.01</v>
       </c>
       <c r="L39" t="n">
-        <v>5.05</v>
+        <v>5.69</v>
       </c>
       <c r="M39" t="n">
         <v>1.56</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>4.12</v>
       </c>
       <c r="O39" t="n">
         <v>-4.33</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.23</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44334</v>
+        <v>44335</v>
       </c>
       <c r="H40" t="n">
-        <v>526.45</v>
+        <v>518.45</v>
       </c>
       <c r="I40" t="n">
         <v>520.9272288830499</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.03</v>
+        <v>-5.49</v>
       </c>
       <c r="L40" t="n">
-        <v>5.33</v>
+        <v>5.84</v>
       </c>
       <c r="M40" t="n">
         <v>1.25</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.15</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44404</v>
+        <v>44405</v>
       </c>
       <c r="H41" t="n">
-        <v>530.6</v>
+        <v>557.45</v>
       </c>
       <c r="I41" t="n">
         <v>541.1670208581208</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.34</v>
+        <v>-7.52</v>
       </c>
       <c r="L41" t="n">
-        <v>6.14</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1.57</v>
       </c>
       <c r="N41" t="n">
-        <v>3.98</v>
+        <v>5.06</v>
       </c>
       <c r="O41" t="n">
         <v>-1.52</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44533</v>
+        <v>44536</v>
       </c>
       <c r="H42" t="n">
-        <v>718.35</v>
+        <v>697.6</v>
       </c>
       <c r="I42" t="n">
         <v>704.6881126443698</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K42" t="n">
-        <v>28.86</v>
+        <v>25.14</v>
       </c>
       <c r="L42" t="n">
         <v>5.29</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.25</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44566</v>
+        <v>44567</v>
       </c>
       <c r="H43" t="n">
-        <v>700</v>
+        <v>710.4</v>
       </c>
       <c r="I43" t="n">
         <v>709.9694765247691</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.34</v>
+        <v>-1.83</v>
       </c>
       <c r="L43" t="n">
         <v>3.78</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.07</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H44" t="n">
-        <v>704.4</v>
+        <v>670.9</v>
       </c>
       <c r="I44" t="n">
         <v>686.7444981556873</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.84</v>
+        <v>-5.56</v>
       </c>
       <c r="L44" t="n">
-        <v>4.65</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>2.22</v>
+        <v>3.18</v>
       </c>
       <c r="N44" t="n">
-        <v>3.56</v>
+        <v>4.76</v>
       </c>
       <c r="O44" t="n">
         <v>1.49</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H45" t="n">
-        <v>712</v>
+        <v>722.9</v>
       </c>
       <c r="I45" t="n">
         <v>721.6377132417382</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.13</v>
+        <v>-7.75</v>
       </c>
       <c r="L45" t="n">
-        <v>6.65</v>
+        <v>8.5</v>
       </c>
       <c r="M45" t="n">
         <v>1.22</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.99</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H46" t="n">
-        <v>718.95</v>
+        <v>710.25</v>
       </c>
       <c r="I46" t="n">
         <v>716.2975402601689</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.55</v>
+        <v>-1.75</v>
       </c>
       <c r="L46" t="n">
         <v>3.47</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44771</v>
+        <v>44774</v>
       </c>
       <c r="H47" t="n">
-        <v>677.95</v>
+        <v>694.45</v>
       </c>
       <c r="I47" t="n">
         <v>693.7068687896539</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K47" t="n">
-        <v>4.55</v>
+        <v>2.22</v>
       </c>
       <c r="L47" t="n">
         <v>3.48</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.61</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44922</v>
+        <v>44923</v>
       </c>
       <c r="H48" t="n">
-        <v>814.8</v>
+        <v>803.8</v>
       </c>
       <c r="I48" t="n">
         <v>805.398264578046</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K48" t="n">
-        <v>17.33</v>
+        <v>15.75</v>
       </c>
       <c r="L48" t="n">
         <v>2.51</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45043</v>
+        <v>45044</v>
       </c>
       <c r="H49" t="n">
-        <v>786.5</v>
+        <v>799.3</v>
       </c>
       <c r="I49" t="n">
         <v>789.8461805724461</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K49" t="n">
-        <v>2.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L49" t="n">
         <v>2.77</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.79</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H50" t="n">
-        <v>922.6</v>
+        <v>905.5</v>
       </c>
       <c r="I50" t="n">
         <v>915.4806321622773</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K50" t="n">
-        <v>15.43</v>
+        <v>13.29</v>
       </c>
       <c r="L50" t="n">
         <v>3.21</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.57</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45247</v>
+        <v>45250</v>
       </c>
       <c r="H51" t="n">
-        <v>947.3</v>
+        <v>961.4</v>
       </c>
       <c r="I51" t="n">
         <v>951.1741131921364</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.62</v>
+        <v>-6.17</v>
       </c>
       <c r="L51" t="n">
-        <v>5.36</v>
+        <v>6.49</v>
       </c>
       <c r="M51" t="n">
         <v>1.39</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.69</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H52" t="n">
-        <v>988.45</v>
+        <v>971.55</v>
       </c>
       <c r="I52" t="n">
         <v>985.9951582221578</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>2.81</v>
+        <v>1.06</v>
       </c>
       <c r="L52" t="n">
         <v>2.02</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.24</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45287</v>
+        <v>45288</v>
       </c>
       <c r="H53" t="n">
-        <v>1021.2</v>
+        <v>1036.7</v>
       </c>
       <c r="I53" t="n">
         <v>1022.97715912832</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.11</v>
+        <v>-6.71</v>
       </c>
       <c r="L53" t="n">
-        <v>5.4</v>
+        <v>7.25</v>
       </c>
       <c r="M53" t="n">
         <v>0.55</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.83</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H54" t="n">
-        <v>1391.1</v>
+        <v>1299.7</v>
       </c>
       <c r="I54" t="n">
         <v>1311.101990428036</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K54" t="n">
-        <v>34.19</v>
+        <v>25.37</v>
       </c>
       <c r="L54" t="n">
         <v>2.86</v>
@@ -3519,7 +4166,7 @@
         <v>1.55</v>
       </c>
       <c r="N54" t="n">
-        <v>3.24</v>
+        <v>6.57</v>
       </c>
       <c r="O54" t="n">
         <v>1.52</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>11.19</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45468</v>
+        <v>45469</v>
       </c>
       <c r="H55" t="n">
-        <v>1414.95</v>
+        <v>1459.5</v>
       </c>
       <c r="I55" t="n">
         <v>1445.108044454934</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.869999999999999</v>
+        <v>-12.3</v>
       </c>
       <c r="L55" t="n">
-        <v>12.02</v>
+        <v>13.87</v>
       </c>
       <c r="M55" t="n">
         <v>2</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.34</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H56" t="n">
-        <v>1673.45</v>
+        <v>1640.9</v>
       </c>
       <c r="I56" t="n">
         <v>1659.922746788</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
-        <v>14.66</v>
+        <v>12.43</v>
       </c>
       <c r="L56" t="n">
         <v>3.5</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.74</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H57" t="n">
-        <v>1627.15</v>
+        <v>1643.6</v>
       </c>
       <c r="I57" t="n">
         <v>1630.311644672591</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K57" t="n">
-        <v>0.84</v>
+        <v>-0.16</v>
       </c>
       <c r="L57" t="n">
         <v>6.18</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.24</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="H58" t="n">
-        <v>1639.25</v>
+        <v>1601.3</v>
       </c>
       <c r="I58" t="n">
         <v>1608.178563762137</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.26</v>
+        <v>-2.57</v>
       </c>
       <c r="L58" t="n">
         <v>4.88</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.71</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H59" t="n">
-        <v>1637.15</v>
+        <v>1705.25</v>
       </c>
       <c r="I59" t="n">
         <v>1695.692529687894</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.24</v>
+        <v>-6.49</v>
       </c>
       <c r="L59" t="n">
         <v>7.2</v>
@@ -3804,7 +4511,7 @@
         <v>1.63</v>
       </c>
       <c r="N59" t="n">
-        <v>2.72</v>
+        <v>4.16</v>
       </c>
       <c r="O59" t="n">
         <v>-2.32</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H60" t="n">
-        <v>1964.5</v>
+        <v>1921.9</v>
       </c>
       <c r="I60" t="n">
         <v>1936.102927099749</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K60" t="n">
-        <v>15.2</v>
+        <v>12.7</v>
       </c>
       <c r="L60" t="n">
         <v>3.47</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.45</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="H61" t="n">
-        <v>1941.1</v>
+        <v>1962.4</v>
       </c>
       <c r="I61" t="n">
         <v>1957.796133976595</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K61" t="n">
-        <v>-1</v>
+        <v>-2.11</v>
       </c>
       <c r="L61" t="n">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="M61" t="n">
         <v>1.43</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>4.95</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="H62" t="n">
-        <v>1878.4</v>
+        <v>1867.6</v>
       </c>
       <c r="I62" t="n">
         <v>1870.133445975747</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.28</v>
+        <v>-4.83</v>
       </c>
       <c r="L62" t="n">
-        <v>4.44</v>
+        <v>5.43</v>
       </c>
       <c r="M62" t="n">
         <v>0.66</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>4.36</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="H63" t="n">
-        <v>1939.9</v>
+        <v>1954.9</v>
       </c>
       <c r="I63" t="n">
         <v>1948.983474033483</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.87</v>
+        <v>-4.67</v>
       </c>
       <c r="L63" t="n">
-        <v>5.09</v>
+        <v>5.26</v>
       </c>
       <c r="M63" t="n">
         <v>0.08</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>4.52</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H64" t="n">
-        <v>2094.9</v>
+        <v>2001.2</v>
       </c>
       <c r="I64" t="n">
         <v>2007.221213541343</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>7.16</v>
+        <v>2.37</v>
       </c>
       <c r="L64" t="n">
         <v>0.97</v>
       </c>
       <c r="M64" t="n">
-        <v>1.46</v>
+        <v>2.24</v>
       </c>
       <c r="N64" t="n">
-        <v>1.74</v>
+        <v>4.47</v>
       </c>
       <c r="O64" t="n">
         <v>0.77</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.64</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H65" t="n">
-        <v>2112.2</v>
+        <v>2149.2</v>
       </c>
       <c r="I65" t="n">
         <v>2140.579085328362</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>-5.55</v>
+        <v>-7.4</v>
       </c>
       <c r="L65" t="n">
-        <v>6.04</v>
+        <v>7.89</v>
       </c>
       <c r="M65" t="n">
         <v>1.26</v>
       </c>
       <c r="N65" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="O65" t="n">
         <v>-4.47</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>6.14</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="H66" t="n">
-        <v>2067</v>
+        <v>2053.2</v>
       </c>
       <c r="I66" t="n">
         <v>2058.184177229914</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.82</v>
+        <v>-4.47</v>
       </c>
       <c r="L66" t="n">
-        <v>4.05</v>
+        <v>5.17</v>
       </c>
       <c r="M66" t="n">
         <v>2.66</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.72</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H67" t="n">
-        <v>1883.5</v>
+        <v>1905.4</v>
       </c>
       <c r="I67" t="n">
         <v>1887.025564006206</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K67" t="n">
-        <v>8.27</v>
+        <v>7.2</v>
       </c>
       <c r="L67" t="n">
         <v>5.4</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>6</v>
+      </c>
+      <c r="U67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.72</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H68" t="n">
-        <v>1799</v>
+        <v>1775.2</v>
       </c>
       <c r="I68" t="n">
         <v>1781.361409709976</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.58</v>
+        <v>-6.83</v>
       </c>
       <c r="L68" t="n">
         <v>7.05</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>7.49</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="H69" t="n">
-        <v>1874.8</v>
+        <v>1910.8</v>
       </c>
       <c r="I69" t="n">
         <v>1897.5028728529</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K69" t="n">
-        <v>-5.61</v>
+        <v>-7.64</v>
       </c>
       <c r="L69" t="n">
-        <v>5.84</v>
+        <v>8.02</v>
       </c>
       <c r="M69" t="n">
         <v>1.02</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.73</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H70" t="n">
-        <v>1882.4</v>
+        <v>1811.9</v>
       </c>
       <c r="I70" t="n">
         <v>1875.70396904765</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.49</v>
+        <v>-5.18</v>
       </c>
       <c r="L70" t="n">
-        <v>4.07</v>
+        <v>5.18</v>
       </c>
       <c r="M70" t="n">
         <v>1.6</v>
       </c>
       <c r="N70" t="n">
-        <v>2.31</v>
+        <v>3.75</v>
       </c>
       <c r="O70" t="n">
         <v>1.92</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>8.58</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H71" t="n">
-        <v>1794.6</v>
+        <v>1854</v>
       </c>
       <c r="I71" t="n">
         <v>1838.610744393591</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K71" t="n">
-        <v>0.95</v>
+        <v>-2.32</v>
       </c>
       <c r="L71" t="n">
         <v>4.61</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,14 @@
       <c r="Q72" t="n">
         <v>9</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9506,7 +10377,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.8</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="6">
@@ -9516,7 +10387,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9526,7 +10397,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -9536,7 +10407,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9546,7 +10417,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.8</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="10">
@@ -9556,7 +10427,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="11">
@@ -9566,7 +10437,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -9576,7 +10447,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -9586,7 +10457,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="14">
@@ -9596,7 +10467,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="15">
@@ -9606,7 +10477,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.14</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="16">
@@ -9616,7 +10487,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.14</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="17">
@@ -9626,7 +10497,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.91</v>
+        <v>34.69</v>
       </c>
     </row>
     <row r="18">
@@ -9636,7 +10507,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.7</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="19">
@@ -9646,7 +10517,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.71</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="20">
@@ -9656,7 +10527,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="21">
@@ -9666,7 +10537,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.86</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="22">
@@ -9676,7 +10547,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -9686,7 +10557,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -9696,7 +10567,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25">
@@ -9706,7 +10577,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.3</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="26">
@@ -9716,7 +10587,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.91</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="27">
@@ -9736,7 +10607,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
